--- a/ModExcel/J角色初始数据表.xlsx
+++ b/ModExcel/J角色初始数据表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\survivors\data\Mod表格数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EB2B4D-264C-4E97-8CAE-DC2839C682CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70329BE8-D6BB-4ABD-8693-A527851E8C96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -942,6 +942,34 @@
     <t>position_priority_i</t>
   </si>
   <si>
+    <t>106:600</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>107:900</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>106:1200</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>106:1800</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>106:2400</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>106:3000</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>106:3600</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">解锁职业数量
 流水号
 </t>
@@ -1047,34 +1075,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>4:10801;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4:10301;5:11101;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4:11501;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4:10901;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4:10401;5:10401;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4:10501;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>4:10701;11:20001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>101:32;102:17;103:7;104:9;220:150;240:20;241:30;242:20;300:100;303:100;309:500;323:10;406:3;408:1;411:400;417:1;419:500;420:200;803:50;804:50;807:100;808:50;809:100;810:100;435:6;814:100;815:100</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1151,6 +1151,34 @@
   </si>
   <si>
     <t>51606</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:10801;11:21001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:10301;5:11101;11:21001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:11501;11:21001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:10901;11:21001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:10401;5:10401;11:21001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:10501;11:21001</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>4:10701;11:21001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1238,7 +1266,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1249,6 +1277,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
     <fill>
@@ -1357,7 +1391,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1404,19 +1438,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1428,40 +1462,49 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2682,7 +2725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AS17"/>
+  <dimension ref="A1:AS36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.375" style="1" customWidth="1"/>
@@ -2788,49 +2831,49 @@
       </c>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="34" t="s">
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="33" t="s">
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="35" t="s">
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="Y7" s="35"/>
-      <c r="Z7" s="35"/>
-      <c r="AA7" s="35"/>
-      <c r="AB7" s="31" t="s">
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="AC7" s="31"/>
-      <c r="AD7" s="31"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="34"/>
       <c r="AE7" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="AF7" s="32" t="s">
+      <c r="AF7" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="AG7" s="32"/>
-      <c r="AH7" s="32"/>
-      <c r="AI7" s="32"/>
-      <c r="AJ7" s="32"/>
+      <c r="AG7" s="35"/>
+      <c r="AH7" s="35"/>
+      <c r="AI7" s="35"/>
+      <c r="AJ7" s="35"/>
       <c r="AK7" s="17" t="s">
         <v>69</v>
       </c>
@@ -2940,7 +2983,7 @@
         <v>110</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AJ8" s="18" t="s">
         <v>33</v>
@@ -3164,7 +3207,7 @@
         <v>173</v>
       </c>
       <c r="AL10" s="15" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AM10" s="21" t="s">
         <v>115</v>
@@ -3197,10 +3240,10 @@
       <c r="G11" s="9">
         <v>60102</v>
       </c>
-      <c r="H11" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="I11" s="28" t="s">
+      <c r="H11" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="I11" s="30" t="s">
         <v>184</v>
       </c>
       <c r="J11" s="9">
@@ -3282,7 +3325,7 @@
         <v>174</v>
       </c>
       <c r="AL11" s="15" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="AM11" s="21" t="s">
         <v>116</v>
@@ -3315,10 +3358,10 @@
       <c r="G12" s="9">
         <v>60103</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="30" t="s">
         <v>191</v>
       </c>
       <c r="J12" s="9">
@@ -3398,7 +3441,7 @@
         <v>188</v>
       </c>
       <c r="AL12" s="15" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="AM12" s="21" t="s">
         <v>117</v>
@@ -3431,10 +3474,10 @@
       <c r="G13" s="9">
         <v>60104</v>
       </c>
-      <c r="H13" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="I13" s="28" t="s">
+      <c r="H13" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" s="30" t="s">
         <v>187</v>
       </c>
       <c r="J13" s="9">
@@ -3512,7 +3555,7 @@
         <v>175</v>
       </c>
       <c r="AL13" s="15" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="AM13" s="21" t="s">
         <v>118</v>
@@ -3545,10 +3588,10 @@
       <c r="G14" s="9">
         <v>60105</v>
       </c>
-      <c r="H14" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="I14" s="28" t="s">
+      <c r="H14" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="30" t="s">
         <v>185</v>
       </c>
       <c r="J14" s="9">
@@ -3594,7 +3637,7 @@
         <v>1034001</v>
       </c>
       <c r="X14" s="13" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Y14" s="13"/>
       <c r="Z14" s="13"/>
@@ -3626,10 +3669,10 @@
         <v>176</v>
       </c>
       <c r="AL14" s="15" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="AM14" s="21" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="AO14" s="7" t="s">
         <v>94</v>
@@ -3659,10 +3702,10 @@
       <c r="G15" s="9">
         <v>60106</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="30" t="s">
         <v>192</v>
       </c>
       <c r="J15" s="9">
@@ -3740,7 +3783,7 @@
         <v>177</v>
       </c>
       <c r="AL15" s="15" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="AM15" s="21" t="s">
         <v>119</v>
@@ -3773,10 +3816,10 @@
       <c r="G16" s="9">
         <v>60107</v>
       </c>
-      <c r="H16" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="I16" s="29" t="s">
+      <c r="H16" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I16" s="32" t="s">
         <v>186</v>
       </c>
       <c r="J16" s="9">
@@ -3804,14 +3847,14 @@
         <v>101</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="S16" s="23">
         <v>1090201</v>
       </c>
-      <c r="T16" s="27"/>
+      <c r="T16" s="29"/>
       <c r="U16" s="1" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="V16" s="10">
         <v>1073001</v>
@@ -3831,7 +3874,7 @@
       <c r="AE16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AF16" s="24">
+      <c r="AF16" s="25">
         <v>30004</v>
       </c>
       <c r="AG16" s="1" t="s">
@@ -3850,10 +3893,10 @@
         <v>178</v>
       </c>
       <c r="AL16" s="15" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="AM16" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="AO16" s="7" t="s">
         <v>96</v>
@@ -3883,10 +3926,10 @@
       <c r="G17" s="9">
         <v>60108</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="I17" s="29" t="s">
+      <c r="H17" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="32" t="s">
         <v>186</v>
       </c>
       <c r="J17" s="9">
@@ -3914,16 +3957,16 @@
         <v>104</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="S17" s="23">
         <v>1092102</v>
       </c>
-      <c r="T17" s="27">
+      <c r="T17" s="29">
         <v>0</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="V17" s="10">
         <v>1083001</v>
@@ -3943,7 +3986,7 @@
       <c r="AE17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AF17" s="24">
+      <c r="AF17" s="25">
         <v>30004</v>
       </c>
       <c r="AG17" s="1" t="s">
@@ -3962,10 +4005,10 @@
         <v>179</v>
       </c>
       <c r="AL17" s="15" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="AM17" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="AO17" s="7" t="s">
         <v>97</v>
@@ -3975,6 +4018,151 @@
         <v>105</v>
       </c>
       <c r="AS17" s="2"/>
+    </row>
+    <row r="18" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="C18" s="3"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="4"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="24"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="14"/>
+      <c r="AI18" s="14"/>
+      <c r="AJ18" s="13"/>
+      <c r="AL18" s="15"/>
+      <c r="AM18" s="7"/>
+    </row>
+    <row r="19" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H19" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H20" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="14"/>
+      <c r="AK20" s="2"/>
+    </row>
+    <row r="21" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H21" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" s="14"/>
+      <c r="AK21" s="2"/>
+    </row>
+    <row r="22" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H22" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="14"/>
+      <c r="AK22" s="2"/>
+    </row>
+    <row r="23" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H23" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="I23" s="14"/>
+      <c r="AK23" s="2"/>
+    </row>
+    <row r="24" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H24" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="AK24" s="2"/>
+    </row>
+    <row r="25" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="AK25" s="2"/>
+    </row>
+    <row r="26" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="AK26" s="2"/>
+    </row>
+    <row r="27" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H28" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="30"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H29" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="I29" s="31"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H30" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I30" s="30"/>
+      <c r="AK30" s="2"/>
+    </row>
+    <row r="31" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H31" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="I31" s="31"/>
+      <c r="AK31" s="2"/>
+    </row>
+    <row r="32" spans="2:45" x14ac:dyDescent="0.15">
+      <c r="H32" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I32" s="30"/>
+      <c r="AK32" s="2"/>
+    </row>
+    <row r="33" spans="8:37" x14ac:dyDescent="0.15">
+      <c r="H33" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="I33" s="31"/>
+      <c r="AK33" s="2"/>
+    </row>
+    <row r="34" spans="8:37" x14ac:dyDescent="0.15">
+      <c r="H34" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="I34" s="30"/>
+    </row>
+    <row r="35" spans="8:37" x14ac:dyDescent="0.15">
+      <c r="H35" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="I35" s="30"/>
+    </row>
+    <row r="36" spans="8:37" x14ac:dyDescent="0.15">
+      <c r="H36" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4016,7 +4204,7 @@
     <row r="2" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5"/>
       <c r="B2" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -4031,10 +4219,10 @@
     <row r="8" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8"/>
       <c r="C8" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.15">
@@ -4042,7 +4230,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4051,7 +4239,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F10" s="7"/>
       <c r="H10" s="2"/>
@@ -4064,7 +4252,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F11" s="7"/>
       <c r="H11" s="2"/>
@@ -4077,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F12" s="7"/>
       <c r="H12" s="2"/>
@@ -4090,7 +4278,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F13" s="7"/>
       <c r="H13" s="2"/>
@@ -4103,7 +4291,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F14" s="7"/>
       <c r="H14" s="2"/>
@@ -4116,7 +4304,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F15" s="7"/>
       <c r="H15" s="2"/>
@@ -4129,7 +4317,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F16" s="7"/>
       <c r="H16" s="2"/>
@@ -4142,7 +4330,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F17" s="7"/>
       <c r="H17" s="2"/>
